--- a/ig/DM-OCTOBRE-2024/CodeSystem-TRE-R252-TypeHoraire.xlsx
+++ b/ig/DM-OCTOBRE-2024/CodeSystem-TRE-R252-TypeHoraire.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="73">
   <si>
     <t>Property</t>
   </si>
@@ -37,7 +37,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20240628120000</t>
+    <t>20241025120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -64,7 +64,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-28T12:00:00+01:00</t>
+    <t>2024-10-25T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -193,7 +193,10 @@
     <t>05</t>
   </si>
   <si>
-    <t>Horaire de visite d'un acteur de santé</t>
+    <t>Horaire de visite à domicile</t>
+  </si>
+  <si>
+    <t>Horaire d'intervention d'un professionnel de santé au domicile d'un patient ou d'un usager pour assurer une continuité des soins et/ou de la prise en charge, de l'accompagnement</t>
   </si>
   <si>
     <t>06</t>
@@ -218,6 +221,18 @@
   </si>
   <si>
     <t>Horaire à préciser</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>Horaire de téléconsultation</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>Horaire mixte : consultation ou téléconsultation</t>
   </si>
 </sst>
 </file>
@@ -591,7 +606,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:D12"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -666,17 +681,19 @@
       <c r="C6" t="s" s="2">
         <v>59</v>
       </c>
-      <c r="D6" s="2"/>
+      <c r="D6" t="s" s="2">
+        <v>60</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
         <v>49</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C7" t="s" s="2">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D7" s="2"/>
     </row>
@@ -685,10 +702,10 @@
         <v>49</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C8" t="s" s="2">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D8" s="2"/>
     </row>
@@ -697,10 +714,10 @@
         <v>49</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C9" t="s" s="2">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D9" s="2"/>
     </row>
@@ -709,12 +726,36 @@
         <v>49</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C10" t="s" s="2">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D10" s="2"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="s" s="2">
+        <v>49</v>
+      </c>
+      <c r="B11" t="s" s="2">
+        <v>69</v>
+      </c>
+      <c r="C11" t="s" s="2">
+        <v>70</v>
+      </c>
+      <c r="D11" s="2"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="s" s="2">
+        <v>49</v>
+      </c>
+      <c r="B12" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="C12" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="D12" s="2"/>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
